--- a/data-raw/clim1/keys/plot-key-v2.xlsx
+++ b/data-raw/clim1/keys/plot-key-v2.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F213"/>
+  <dimension ref="A1:E213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -380,25 +380,20 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>sea_name</t>
+          <t>block</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>plot</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>plot</t>
+          <t>trt_nu</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>trt_nu</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
         <is>
           <t>trt_name</t>
         </is>
@@ -412,21 +407,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>101</v>
       </c>
       <c r="D2">
-        <v>101</v>
-      </c>
-      <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>PRACTICE PLOT</t>
         </is>
@@ -440,21 +430,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D3">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C3">
         <v>102</v>
       </c>
+      <c r="D3" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F3" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -466,21 +451,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D4">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C4">
         <v>103</v>
       </c>
+      <c r="D4" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F4" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -492,21 +472,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D5">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C5">
         <v>104</v>
       </c>
+      <c r="D5" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F5" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -518,21 +493,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D6">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C6">
         <v>105</v>
       </c>
+      <c r="D6" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F6" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -544,22 +514,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>106</v>
       </c>
       <c r="D7">
-        <v>106</v>
-      </c>
-      <c r="E7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F7" t="e">
-        <v>#N/A</v>
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>26s_pbuckwide</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -570,24 +537,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D8">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C8">
         <v>107</v>
       </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>26s_p</t>
-        </is>
+      <c r="D8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E8" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="9">
@@ -598,21 +558,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D9">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C9">
         <v>108</v>
       </c>
+      <c r="D9" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F9" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -624,21 +579,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D10">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C10">
         <v>109</v>
       </c>
+      <c r="D10" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F10" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -650,21 +600,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D11">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C11">
         <v>110</v>
       </c>
+      <c r="D11" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F11" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -676,21 +621,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D12">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C12">
         <v>111</v>
       </c>
+      <c r="D12" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F12" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -702,21 +642,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D13">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C13">
         <v>112</v>
       </c>
+      <c r="D13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F13" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -728,22 +663,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>113</v>
       </c>
       <c r="D14">
-        <v>113</v>
-      </c>
-      <c r="E14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F14" t="e">
-        <v>#N/A</v>
+        <v>6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>26s_w</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -754,21 +686,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D15">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C15">
         <v>114</v>
       </c>
+      <c r="D15" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F15" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -780,22 +707,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>115</v>
       </c>
       <c r="D16">
-        <v>115</v>
-      </c>
-      <c r="E16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F16" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>26s_p</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -806,21 +730,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D17">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C17">
         <v>116</v>
       </c>
+      <c r="D17" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F17" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -832,21 +751,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D18">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C18">
         <v>117</v>
       </c>
+      <c r="D18" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F18" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -858,22 +772,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>118</v>
       </c>
       <c r="D19">
-        <v>118</v>
-      </c>
-      <c r="E19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F19" t="e">
-        <v>#N/A</v>
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>26s_pbuck</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -884,21 +795,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D20">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C20">
         <v>119</v>
       </c>
+      <c r="D20" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F20" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -910,21 +816,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D21">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C21">
         <v>120</v>
       </c>
+      <c r="D21" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F21" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -936,21 +837,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D22">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C22">
         <v>121</v>
       </c>
+      <c r="D22" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F22" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -962,21 +858,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D23">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C23">
         <v>122</v>
       </c>
+      <c r="D23" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F23" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -988,21 +879,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D24">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C24">
         <v>123</v>
       </c>
+      <c r="D24" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F24" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1014,21 +900,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D25">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C25">
         <v>124</v>
       </c>
+      <c r="D25" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F25" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1040,22 +921,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>125</v>
       </c>
       <c r="D26">
-        <v>125</v>
-      </c>
-      <c r="E26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F26" t="e">
-        <v>#N/A</v>
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>26s_pleg1</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1066,21 +944,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D27">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C27">
         <v>126</v>
       </c>
+      <c r="D27" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F27" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1092,21 +965,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D28">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C28">
         <v>127</v>
       </c>
+      <c r="D28" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F28" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1118,21 +986,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D29">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C29">
         <v>128</v>
       </c>
+      <c r="D29" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F29" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1144,21 +1007,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D30">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C30">
         <v>129</v>
       </c>
+      <c r="D30" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F30" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1170,24 +1028,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D31">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C31">
         <v>130</v>
       </c>
-      <c r="E31">
-        <v>2</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>26s_pleg1</t>
-        </is>
+      <c r="D31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E31" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="32">
@@ -1198,21 +1049,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D32">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C32">
         <v>131</v>
       </c>
+      <c r="D32" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F32" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1224,21 +1070,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D33">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C33">
         <v>132</v>
       </c>
+      <c r="D33" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F33" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1250,24 +1091,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D34">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C34">
         <v>133</v>
       </c>
-      <c r="E34">
-        <v>6</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>26s_w</t>
-        </is>
+      <c r="D34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E34" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="35">
@@ -1278,21 +1112,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D35">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C35">
         <v>134</v>
       </c>
+      <c r="D35" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F35" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1304,24 +1133,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D36">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C36">
         <v>135</v>
       </c>
-      <c r="E36">
-        <v>5</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>26s_pbuckwide</t>
-        </is>
+      <c r="D36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E36" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="37">
@@ -1332,21 +1154,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D37">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C37">
         <v>136</v>
       </c>
+      <c r="D37" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F37" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1358,24 +1175,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D38">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C38">
         <v>137</v>
       </c>
-      <c r="E38">
-        <v>3</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>26s_pleg2wide</t>
-        </is>
+      <c r="D38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E38" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="39">
@@ -1386,21 +1196,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D39">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C39">
         <v>138</v>
       </c>
+      <c r="D39" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F39" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1412,22 +1217,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>139</v>
       </c>
       <c r="D40">
-        <v>139</v>
-      </c>
-      <c r="E40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F40" t="e">
-        <v>#N/A</v>
+        <v>3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>26s_pleg2wide</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1438,21 +1240,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D41">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C41">
         <v>140</v>
       </c>
+      <c r="D41" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F41" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1464,21 +1261,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D42">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C42">
         <v>141</v>
       </c>
+      <c r="D42" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F42" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1490,24 +1282,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D43">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C43">
         <v>142</v>
       </c>
-      <c r="E43">
-        <v>4</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>26s_pbuck</t>
-        </is>
+      <c r="D43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E43" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="44">
@@ -1518,21 +1303,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D44">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C44">
         <v>143</v>
       </c>
+      <c r="D44" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F44" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1544,21 +1324,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D45">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C45">
         <v>144</v>
       </c>
+      <c r="D45" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F45" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1570,21 +1345,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D46">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C46">
         <v>145</v>
       </c>
+      <c r="D46" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F46" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1596,21 +1366,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D47">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C47">
         <v>146</v>
       </c>
+      <c r="D47" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F47" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1622,21 +1387,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D48">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C48">
         <v>147</v>
       </c>
+      <c r="D48" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F48" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1648,21 +1408,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D49">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C49">
         <v>148</v>
       </c>
+      <c r="D49" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F49" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1674,21 +1429,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D50">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C50">
         <v>149</v>
       </c>
+      <c r="D50" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F50" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1700,21 +1450,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D51">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C51">
         <v>150</v>
       </c>
+      <c r="D51" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F51" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1726,21 +1471,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D52">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C52">
         <v>151</v>
       </c>
+      <c r="D52" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F52" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1752,21 +1492,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="D53">
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C53">
         <v>152</v>
       </c>
+      <c r="D53" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F53" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1778,21 +1513,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>153</v>
       </c>
       <c r="D54">
-        <v>153</v>
-      </c>
-      <c r="E54">
         <v>0</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>PRACTICE PLOT</t>
         </is>
@@ -1806,21 +1536,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>201</v>
       </c>
       <c r="D55">
-        <v>201</v>
-      </c>
-      <c r="E55">
         <v>0</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>PRACTICE PLOT</t>
         </is>
@@ -1834,22 +1559,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>202</v>
       </c>
       <c r="D56">
-        <v>202</v>
-      </c>
-      <c r="E56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F56" t="e">
-        <v>#N/A</v>
+        <v>5</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>26s_pbuckwide</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1860,24 +1582,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D57">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C57">
         <v>203</v>
       </c>
-      <c r="E57">
-        <v>4</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>26s_pbuck</t>
-        </is>
+      <c r="D57" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E57" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="58">
@@ -1888,21 +1603,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D58">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C58">
         <v>204</v>
       </c>
+      <c r="D58" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F58" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1914,21 +1624,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D59">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C59">
         <v>205</v>
       </c>
+      <c r="D59" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F59" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1940,22 +1645,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>206</v>
       </c>
       <c r="D60">
-        <v>206</v>
-      </c>
-      <c r="E60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F60" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>26s_p</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1966,21 +1668,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D61">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C61">
         <v>207</v>
       </c>
+      <c r="D61" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F61" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1992,21 +1689,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D62">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C62">
         <v>208</v>
       </c>
+      <c r="D62" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F62" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2018,21 +1710,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D63">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C63">
         <v>209</v>
       </c>
+      <c r="D63" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F63" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2044,22 +1731,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>210</v>
       </c>
       <c r="D64">
-        <v>210</v>
-      </c>
-      <c r="E64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F64" t="e">
-        <v>#N/A</v>
+        <v>6</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>26s_w</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -2070,21 +1754,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D65">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C65">
         <v>211</v>
       </c>
+      <c r="D65" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F65" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2096,21 +1775,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D66">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C66">
         <v>212</v>
       </c>
+      <c r="D66" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F66" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2122,21 +1796,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D67">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C67">
         <v>213</v>
       </c>
+      <c r="D67" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F67" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2148,21 +1817,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D68">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C68">
         <v>214</v>
       </c>
+      <c r="D68" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F68" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2174,21 +1838,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D69">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C69">
         <v>215</v>
       </c>
+      <c r="D69" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F69" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2200,21 +1859,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D70">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C70">
         <v>216</v>
       </c>
+      <c r="D70" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F70" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2226,21 +1880,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D71">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C71">
         <v>217</v>
       </c>
+      <c r="D71" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F71" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2252,21 +1901,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D72">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C72">
         <v>218</v>
       </c>
+      <c r="D72" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F72" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2278,21 +1922,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D73">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C73">
         <v>219</v>
       </c>
+      <c r="D73" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F73" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2304,21 +1943,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D74">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C74">
         <v>220</v>
       </c>
+      <c r="D74" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F74" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2330,21 +1964,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D75">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C75">
         <v>221</v>
       </c>
+      <c r="D75" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F75" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2356,21 +1985,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D76">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C76">
         <v>222</v>
       </c>
+      <c r="D76" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F76" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2382,22 +2006,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>223</v>
       </c>
       <c r="D77">
-        <v>223</v>
-      </c>
-      <c r="E77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F77" t="e">
-        <v>#N/A</v>
+        <v>4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>26s_pbuck</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -2408,21 +2029,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D78">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C78">
         <v>224</v>
       </c>
+      <c r="D78" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F78" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2434,21 +2050,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D79">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C79">
         <v>225</v>
       </c>
+      <c r="D79" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F79" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2460,24 +2071,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D80">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C80">
         <v>226</v>
       </c>
-      <c r="E80">
-        <v>6</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>26s_w</t>
-        </is>
+      <c r="D80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E80" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="81">
@@ -2488,21 +2092,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D81">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C81">
         <v>227</v>
       </c>
+      <c r="D81" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F81" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2514,21 +2113,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D82">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C82">
         <v>228</v>
       </c>
+      <c r="D82" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F82" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2540,21 +2134,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D83">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C83">
         <v>229</v>
       </c>
+      <c r="D83" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F83" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2566,21 +2155,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D84">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C84">
         <v>230</v>
       </c>
+      <c r="D84" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F84" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2592,21 +2176,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D85">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C85">
         <v>231</v>
       </c>
+      <c r="D85" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F85" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2618,24 +2197,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D86">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C86">
         <v>232</v>
       </c>
-      <c r="E86">
-        <v>1</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>26s_p</t>
-        </is>
+      <c r="D86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E86" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="87">
@@ -2646,21 +2218,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D87">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C87">
         <v>233</v>
       </c>
+      <c r="D87" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F87" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2672,21 +2239,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D88">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C88">
         <v>234</v>
       </c>
+      <c r="D88" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F88" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2698,24 +2260,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D89">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C89">
         <v>235</v>
       </c>
-      <c r="E89">
-        <v>5</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>26s_pbuckwide</t>
-        </is>
+      <c r="D89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E89" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="90">
@@ -2726,21 +2281,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D90">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C90">
         <v>236</v>
       </c>
+      <c r="D90" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F90" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2752,21 +2302,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D91">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C91">
         <v>237</v>
       </c>
+      <c r="D91" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F91" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2778,21 +2323,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D92">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C92">
         <v>238</v>
       </c>
+      <c r="D92" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E92" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F92" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2804,21 +2344,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D93">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C93">
         <v>239</v>
       </c>
+      <c r="D93" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E93" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F93" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2830,21 +2365,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D94">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C94">
         <v>240</v>
       </c>
+      <c r="D94" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F94" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2856,21 +2386,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D95">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C95">
         <v>241</v>
       </c>
+      <c r="D95" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F95" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2882,21 +2407,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D96">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C96">
         <v>242</v>
       </c>
+      <c r="D96" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F96" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2908,24 +2428,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D97">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C97">
         <v>243</v>
       </c>
-      <c r="E97">
-        <v>3</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>26s_pleg2wide</t>
-        </is>
+      <c r="D97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E97" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="98">
@@ -2936,21 +2449,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D98">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C98">
         <v>244</v>
       </c>
+      <c r="D98" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F98" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2962,21 +2470,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D99">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C99">
         <v>245</v>
       </c>
+      <c r="D99" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F99" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2988,21 +2491,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D100">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C100">
         <v>246</v>
       </c>
+      <c r="D100" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F100" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3014,22 +2512,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>247</v>
       </c>
       <c r="D101">
-        <v>247</v>
-      </c>
-      <c r="E101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F101" t="e">
-        <v>#N/A</v>
+        <v>3</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>26s_pleg2wide</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -3040,24 +2535,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D102">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C102">
         <v>248</v>
       </c>
-      <c r="E102">
-        <v>2</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>26s_pleg1</t>
-        </is>
+      <c r="D102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E102" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="103">
@@ -3068,21 +2556,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D103">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C103">
         <v>249</v>
       </c>
+      <c r="D103" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F103" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3094,21 +2577,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D104">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C104">
         <v>250</v>
       </c>
+      <c r="D104" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F104" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3120,21 +2598,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="D105">
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C105">
         <v>251</v>
       </c>
+      <c r="D105" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F105" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3146,22 +2619,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>252</v>
       </c>
       <c r="D106">
-        <v>252</v>
-      </c>
-      <c r="E106" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F106" t="e">
-        <v>#N/A</v>
+        <v>2</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>26s_pleg1</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -3172,21 +2642,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>253</v>
       </c>
       <c r="D107">
-        <v>253</v>
-      </c>
-      <c r="E107">
         <v>0</v>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>PRACTICE PLOT</t>
         </is>
@@ -3200,21 +2665,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>301</v>
       </c>
       <c r="D108">
-        <v>301</v>
-      </c>
-      <c r="E108">
         <v>0</v>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>PRACTICE PLOT</t>
         </is>
@@ -3228,21 +2688,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D109">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C109">
         <v>302</v>
       </c>
+      <c r="D109" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E109" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F109" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3254,21 +2709,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D110">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C110">
         <v>303</v>
       </c>
+      <c r="D110" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F110" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3280,21 +2730,16 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D111">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C111">
         <v>304</v>
       </c>
+      <c r="D111" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F111" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3306,21 +2751,16 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D112">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C112">
         <v>305</v>
       </c>
+      <c r="D112" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F112" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3332,21 +2772,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D113">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C113">
         <v>306</v>
       </c>
+      <c r="D113" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E113" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F113" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3358,22 +2793,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>307</v>
       </c>
       <c r="D114">
-        <v>307</v>
-      </c>
-      <c r="E114" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F114" t="e">
-        <v>#N/A</v>
+        <v>6</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>26s_w</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -3384,21 +2816,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D115">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C115">
         <v>308</v>
       </c>
+      <c r="D115" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E115" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F115" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3410,21 +2837,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D116">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C116">
         <v>309</v>
       </c>
+      <c r="D116" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E116" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F116" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3436,21 +2858,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D117">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C117">
         <v>310</v>
       </c>
+      <c r="D117" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F117" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3462,21 +2879,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D118">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C118">
         <v>311</v>
       </c>
+      <c r="D118" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F118" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3488,21 +2900,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D119">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C119">
         <v>312</v>
       </c>
+      <c r="D119" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E119" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F119" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3514,22 +2921,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>313</v>
       </c>
       <c r="D120">
-        <v>313</v>
-      </c>
-      <c r="E120" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F120" t="e">
-        <v>#N/A</v>
+        <v>3</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>26s_pleg2wide</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -3540,22 +2944,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>314</v>
       </c>
       <c r="D121">
-        <v>314</v>
-      </c>
-      <c r="E121" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F121" t="e">
-        <v>#N/A</v>
+        <v>5</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>26s_pbuckwide</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -3566,24 +2967,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D122">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C122">
         <v>315</v>
       </c>
-      <c r="E122">
-        <v>6</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>26s_w</t>
-        </is>
+      <c r="D122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E122" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="123">
@@ -3594,21 +2988,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D123">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C123">
         <v>316</v>
       </c>
+      <c r="D123" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E123" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F123" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3620,21 +3009,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D124">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C124">
         <v>317</v>
       </c>
+      <c r="D124" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E124" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F124" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3646,24 +3030,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D125">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C125">
         <v>318</v>
       </c>
-      <c r="E125">
-        <v>3</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>26s_pleg2wide</t>
-        </is>
+      <c r="D125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E125" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="126">
@@ -3674,21 +3051,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D126">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C126">
         <v>319</v>
       </c>
+      <c r="D126" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E126" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F126" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3700,21 +3072,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D127">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C127">
         <v>320</v>
       </c>
+      <c r="D127" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E127" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F127" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3726,21 +3093,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D128">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C128">
         <v>321</v>
       </c>
+      <c r="D128" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E128" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F128" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3752,21 +3114,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D129">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C129">
         <v>322</v>
       </c>
+      <c r="D129" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E129" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F129" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3778,21 +3135,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D130">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C130">
         <v>323</v>
       </c>
+      <c r="D130" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E130" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3804,24 +3156,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D131">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C131">
         <v>324</v>
       </c>
-      <c r="E131">
-        <v>1</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>26s_p</t>
-        </is>
+      <c r="D131" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E131" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="132">
@@ -3832,21 +3177,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D132">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C132">
         <v>325</v>
       </c>
+      <c r="D132" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E132" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F132" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3858,21 +3198,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D133">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C133">
         <v>326</v>
       </c>
+      <c r="D133" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F133" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3884,21 +3219,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D134">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C134">
         <v>327</v>
       </c>
+      <c r="D134" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E134" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F134" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3910,22 +3240,19 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>328</v>
       </c>
       <c r="D135">
-        <v>328</v>
-      </c>
-      <c r="E135" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F135" t="e">
-        <v>#N/A</v>
+        <v>2</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>26s_pleg1</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -3936,24 +3263,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D136">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C136">
         <v>329</v>
       </c>
-      <c r="E136">
-        <v>5</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>26s_pbuckwide</t>
-        </is>
+      <c r="D136" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E136" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="137">
@@ -3964,21 +3284,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D137">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C137">
         <v>330</v>
       </c>
+      <c r="D137" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E137" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F137" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3990,21 +3305,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D138">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C138">
         <v>331</v>
       </c>
+      <c r="D138" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E138" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F138" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4016,21 +3326,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D139">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C139">
         <v>332</v>
       </c>
+      <c r="D139" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E139" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F139" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4042,21 +3347,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D140">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C140">
         <v>333</v>
       </c>
+      <c r="D140" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E140" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F140" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4068,24 +3368,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D141">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C141">
         <v>334</v>
       </c>
-      <c r="E141">
-        <v>4</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>26s_pbuck</t>
-        </is>
+      <c r="D141" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E141" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="142">
@@ -4096,22 +3389,19 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>335</v>
       </c>
       <c r="D142">
-        <v>335</v>
-      </c>
-      <c r="E142" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F142" t="e">
-        <v>#N/A</v>
+        <v>4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>26s_pbuck</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -4122,21 +3412,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D143">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C143">
         <v>336</v>
       </c>
+      <c r="D143" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E143" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F143" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4148,21 +3433,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D144">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C144">
         <v>337</v>
       </c>
+      <c r="D144" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E144" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F144" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4174,21 +3454,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D145">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C145">
         <v>338</v>
       </c>
+      <c r="D145" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F145" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4200,21 +3475,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D146">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C146">
         <v>339</v>
       </c>
+      <c r="D146" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E146" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F146" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4226,21 +3496,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D147">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C147">
         <v>340</v>
       </c>
+      <c r="D147" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E147" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F147" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4252,21 +3517,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D148">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C148">
         <v>341</v>
       </c>
+      <c r="D148" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E148" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F148" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4278,21 +3538,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D149">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C149">
         <v>342</v>
       </c>
+      <c r="D149" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F149" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4304,21 +3559,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D150">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C150">
         <v>343</v>
       </c>
+      <c r="D150" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E150" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F150" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4330,21 +3580,16 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D151">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C151">
         <v>344</v>
       </c>
+      <c r="D151" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E151" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F151" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4356,21 +3601,16 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D152">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C152">
         <v>345</v>
       </c>
+      <c r="D152" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E152" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F152" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4382,24 +3622,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D153">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C153">
         <v>346</v>
       </c>
-      <c r="E153">
-        <v>2</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>26s_pleg1</t>
-        </is>
+      <c r="D153" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E153" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="154">
@@ -4410,21 +3643,16 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D154">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C154">
         <v>347</v>
       </c>
+      <c r="D154" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E154" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F154" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4436,21 +3664,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D155">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C155">
         <v>348</v>
       </c>
+      <c r="D155" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F155" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4462,21 +3685,16 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D156">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C156">
         <v>349</v>
       </c>
+      <c r="D156" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E156" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F156" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4488,22 +3706,19 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>350</v>
       </c>
       <c r="D157">
-        <v>350</v>
-      </c>
-      <c r="E157" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F157" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>26s_p</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -4514,21 +3729,16 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D158">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C158">
         <v>351</v>
       </c>
+      <c r="D158" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E158" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F158" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4540,21 +3750,16 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="D159">
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C159">
         <v>352</v>
       </c>
+      <c r="D159" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E159" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F159" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4566,21 +3771,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>353</v>
       </c>
       <c r="D160">
-        <v>353</v>
-      </c>
-      <c r="E160">
         <v>0</v>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>PRACTICE PLOT</t>
         </is>
@@ -4594,21 +3794,16 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>401</v>
       </c>
       <c r="D161">
-        <v>401</v>
-      </c>
-      <c r="E161">
         <v>0</v>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>PRACTICE PLOT</t>
         </is>
@@ -4622,21 +3817,16 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D162">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C162">
         <v>402</v>
       </c>
+      <c r="D162" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E162" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F162" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4648,21 +3838,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D163">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C163">
         <v>403</v>
       </c>
+      <c r="D163" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E163" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F163" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4674,21 +3859,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D164">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C164">
         <v>404</v>
       </c>
+      <c r="D164" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E164" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F164" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4700,21 +3880,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D165">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C165">
         <v>405</v>
       </c>
+      <c r="D165" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E165" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F165" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4726,21 +3901,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D166">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C166">
         <v>406</v>
       </c>
+      <c r="D166" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E166" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F166" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4752,21 +3922,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D167">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C167">
         <v>407</v>
       </c>
+      <c r="D167" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E167" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F167" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4778,21 +3943,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D168">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C168">
         <v>408</v>
       </c>
+      <c r="D168" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E168" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F168" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4804,21 +3964,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D169">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C169">
         <v>409</v>
       </c>
+      <c r="D169" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E169" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F169" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4830,24 +3985,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D170">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C170">
         <v>410</v>
       </c>
-      <c r="E170">
-        <v>4</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>26s_pbuck</t>
-        </is>
+      <c r="D170" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E170" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="171">
@@ -4858,22 +4006,19 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>411</v>
       </c>
       <c r="D171">
-        <v>411</v>
-      </c>
-      <c r="E171" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F171" t="e">
-        <v>#N/A</v>
+        <v>3</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>26s_pleg2wide</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -4884,21 +4029,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D172">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C172">
         <v>412</v>
       </c>
+      <c r="D172" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E172" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F172" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4910,21 +4050,16 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D173">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C173">
         <v>413</v>
       </c>
+      <c r="D173" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E173" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F173" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4936,22 +4071,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>414</v>
       </c>
       <c r="D174">
-        <v>414</v>
-      </c>
-      <c r="E174" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F174" t="e">
-        <v>#N/A</v>
+        <v>6</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>26s_w</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -4962,22 +4094,19 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>415</v>
       </c>
       <c r="D175">
-        <v>415</v>
-      </c>
-      <c r="E175" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F175" t="e">
-        <v>#N/A</v>
+        <v>2</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>26s_pleg1</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -4988,22 +4117,19 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>416</v>
       </c>
       <c r="D176">
-        <v>416</v>
-      </c>
-      <c r="E176" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F176" t="e">
-        <v>#N/A</v>
+        <v>4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>26s_pbuck</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -5014,21 +4140,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D177">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C177">
         <v>417</v>
       </c>
+      <c r="D177" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E177" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F177" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5040,21 +4161,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D178">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C178">
         <v>418</v>
       </c>
+      <c r="D178" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E178" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F178" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5066,24 +4182,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D179">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C179">
         <v>419</v>
       </c>
-      <c r="E179">
-        <v>5</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>26s_pbuckwide</t>
-        </is>
+      <c r="D179" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E179" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="180">
@@ -5094,22 +4203,19 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>420</v>
       </c>
       <c r="D180">
-        <v>420</v>
-      </c>
-      <c r="E180" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F180" t="e">
-        <v>#N/A</v>
+        <v>5</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>26s_pbuckwide</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -5120,22 +4226,19 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>421</v>
       </c>
       <c r="D181">
-        <v>421</v>
-      </c>
-      <c r="E181" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F181" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>26s_p</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -5146,21 +4249,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D182">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C182">
         <v>422</v>
       </c>
+      <c r="D182" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E182" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F182" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5172,21 +4270,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D183">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C183">
         <v>423</v>
       </c>
+      <c r="D183" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E183" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F183" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5198,21 +4291,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D184">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C184">
         <v>424</v>
       </c>
+      <c r="D184" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E184" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F184" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5224,21 +4312,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D185">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C185">
         <v>425</v>
       </c>
+      <c r="D185" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E185" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F185" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5250,21 +4333,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D186">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C186">
         <v>426</v>
       </c>
+      <c r="D186" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E186" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F186" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5276,21 +4354,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D187">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C187">
         <v>427</v>
       </c>
+      <c r="D187" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E187" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F187" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5302,21 +4375,16 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D188">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C188">
         <v>428</v>
       </c>
+      <c r="D188" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E188" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F188" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5328,24 +4396,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D189">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C189">
         <v>429</v>
       </c>
-      <c r="E189">
-        <v>1</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>26s_p</t>
-        </is>
+      <c r="D189" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E189" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="190">
@@ -5356,21 +4417,16 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D190">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C190">
         <v>430</v>
       </c>
+      <c r="D190" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E190" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F190" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5382,21 +4438,16 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D191">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C191">
         <v>431</v>
       </c>
+      <c r="D191" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E191" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F191" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5408,21 +4459,16 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D192">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C192">
         <v>432</v>
       </c>
+      <c r="D192" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E192" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F192" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5434,21 +4480,16 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D193">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C193">
         <v>433</v>
       </c>
+      <c r="D193" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E193" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F193" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5460,21 +4501,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D194">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C194">
         <v>434</v>
       </c>
+      <c r="D194" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E194" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F194" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5486,24 +4522,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D195">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C195">
         <v>435</v>
       </c>
-      <c r="E195">
-        <v>6</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>26s_w</t>
-        </is>
+      <c r="D195" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E195" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="196">
@@ -5514,21 +4543,16 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D196">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C196">
         <v>436</v>
       </c>
+      <c r="D196" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E196" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F196" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5540,21 +4564,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D197">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C197">
         <v>437</v>
       </c>
+      <c r="D197" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E197" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F197" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5566,21 +4585,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D198">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C198">
         <v>438</v>
       </c>
+      <c r="D198" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E198" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F198" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5592,21 +4606,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D199">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C199">
         <v>439</v>
       </c>
+      <c r="D199" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E199" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F199" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5618,21 +4627,16 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D200">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C200">
         <v>440</v>
       </c>
+      <c r="D200" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E200" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F200" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5644,21 +4648,16 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D201">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C201">
         <v>441</v>
       </c>
+      <c r="D201" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E201" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F201" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5670,21 +4669,16 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D202">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C202">
         <v>442</v>
       </c>
+      <c r="D202" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E202" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F202" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5696,21 +4690,16 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D203">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C203">
         <v>443</v>
       </c>
+      <c r="D203" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E203" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F203" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5722,21 +4711,16 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D204">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C204">
         <v>444</v>
       </c>
+      <c r="D204" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E204" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F204" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5748,24 +4732,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D205">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C205">
         <v>445</v>
       </c>
-      <c r="E205">
-        <v>3</v>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>26s_pleg2wide</t>
-        </is>
+      <c r="D205" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E205" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="206">
@@ -5776,21 +4753,16 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D206">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C206">
         <v>446</v>
       </c>
+      <c r="D206" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E206" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F206" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5802,21 +4774,16 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D207">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C207">
         <v>447</v>
       </c>
+      <c r="D207" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E207" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F207" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5828,21 +4795,16 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D208">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C208">
         <v>448</v>
       </c>
+      <c r="D208" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E208" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F208" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5854,21 +4816,16 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D209">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C209">
         <v>449</v>
       </c>
+      <c r="D209" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E209" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F209" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5880,21 +4837,16 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D210">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C210">
         <v>450</v>
       </c>
+      <c r="D210" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E210" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F210" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5906,21 +4858,16 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D211">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C211">
         <v>451</v>
       </c>
+      <c r="D211" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="E211" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F211" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5932,24 +4879,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="D212">
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C212">
         <v>452</v>
       </c>
-      <c r="E212">
-        <v>2</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>26s_pleg1</t>
-        </is>
+      <c r="D212" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E212" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="213">
@@ -5960,21 +4900,16 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>26/27</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>453</v>
       </c>
       <c r="D213">
-        <v>453</v>
-      </c>
-      <c r="E213">
         <v>0</v>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>PRACTICE PLOT</t>
         </is>
